--- a/Excel/Result_verifications.xlsx
+++ b/Excel/Result_verifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_Repository\US-EV-Market_Share_EDA\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F32BE4-1EC1-46EB-904E-885A6957E6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9B6921-A25E-444B-9859-DCAB9A2C676A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{37D4BD1B-EFA8-48B0-94E7-16BBE874FF75}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{37D4BD1B-EFA8-48B0-94E7-16BBE874FF75}"/>
   </bookViews>
   <sheets>
     <sheet name="Result_verifications" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="80">
   <si>
     <t>Percentage of vehicles that are EV, PHEV, HEV and gasoline</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1149,19 +1152,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EBAA2C9-8427-44C3-8D4E-A4F0A5BF90AB}">
   <dimension ref="A1:AQ53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="20" width="8.7265625" style="1"/>
-    <col min="21" max="25" width="8.7265625" style="3"/>
-    <col min="26" max="33" width="8.7265625" style="5"/>
-    <col min="34" max="39" width="8.7265625" style="7"/>
-    <col min="40" max="40" width="19.81640625" style="9" customWidth="1"/>
-    <col min="41" max="41" width="8.7265625" style="9"/>
-    <col min="42" max="42" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="8.77734375" style="1"/>
+    <col min="21" max="25" width="8.77734375" style="3"/>
+    <col min="26" max="33" width="8.77734375" style="5"/>
+    <col min="34" max="39" width="8.77734375" style="7"/>
+    <col min="40" max="40" width="19.77734375" style="9" customWidth="1"/>
+    <col min="41" max="41" width="8.77734375" style="9"/>
+    <col min="42" max="42" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1181,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1267,7 +1270,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>-9.6857309301924613E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>-7.585730930192461E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1544,7 +1547,7 @@
         <v>1.4142690698075392E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>-9.7857309301924607E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>2.1714269069807536E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>4.2142690698075396E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1854,7 +1857,7 @@
         <v>-1.6857309301924611E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -1924,7 +1927,7 @@
         <v>-3.1857309301924607E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1994,7 +1997,7 @@
         <v>1.3614269069807538E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>1.3142690698075398E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -2134,7 +2137,7 @@
         <v>-2.7857309301924614E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -2190,6 +2193,9 @@
         <f t="shared" si="3"/>
         <v>0.88047403018239057</v>
       </c>
+      <c r="Z14" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="AN14" s="9" t="s">
         <v>32</v>
       </c>
@@ -2204,7 +2210,7 @@
         <v>1.1314269069807538E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -2274,7 +2280,7 @@
         <v>-8.0857309301924606E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -2344,7 +2350,7 @@
         <v>-2.4857309301924597E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -2414,7 +2420,7 @@
         <v>-8.18573093019246E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -2484,7 +2490,7 @@
         <v>-9.4857309301924608E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -2554,7 +2560,7 @@
         <v>-8.0857309301924606E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -2624,7 +2630,7 @@
         <v>-9.4857309301924608E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -2694,7 +2700,7 @@
         <v>-1.018573093019246E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2764,7 +2770,7 @@
         <v>-6.3857309301924604E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2834,7 +2840,7 @@
         <v>1.8142690698075403E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2904,7 +2910,7 @@
         <v>1.0142690698075399E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -2974,7 +2980,7 @@
         <v>-6.4857309301924607E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -3044,7 +3050,7 @@
         <v>-5.1857309301924608E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -3114,7 +3120,7 @@
         <v>-1.108573093019246E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -3184,7 +3190,7 @@
         <v>-7.585730930192461E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -3254,7 +3260,7 @@
         <v>-7.8857309301924618E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -3324,7 +3330,7 @@
         <v>-8.8857309301924609E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3394,7 +3400,7 @@
         <v>6.1142690698075385E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -3464,7 +3470,7 @@
         <v>-5.1857309301924608E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -3534,7 +3540,7 @@
         <v>6.0142690698075391E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -3604,7 +3610,7 @@
         <v>-7.0857309301924605E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -3674,7 +3680,7 @@
         <v>-7.8573093019246136E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -3744,7 +3750,7 @@
         <v>-4.6857309301924603E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -3814,7 +3820,7 @@
         <v>-1.108573093019246E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -3884,7 +3890,7 @@
         <v>-7.4857309301924607E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -3954,7 +3960,7 @@
         <v>-7.0857309301924605E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -4024,7 +4030,7 @@
         <v>4.4142690698075384E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -4094,7 +4100,7 @@
         <v>-5.4857309301924607E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -4164,7 +4170,7 @@
         <v>-5.0857309301924605E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -4234,7 +4240,7 @@
         <v>-8.2857309301924593E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -4304,7 +4310,7 @@
         <v>-1.048573093019246E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>70</v>
       </c>
@@ -4374,7 +4380,7 @@
         <v>-7.2857309301924602E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>30</v>
       </c>
@@ -4444,7 +4450,7 @@
         <v>-3.4857309301924606E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>71</v>
       </c>
@@ -4514,7 +4520,7 @@
         <v>6.1426906980753884E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>72</v>
       </c>
@@ -4584,7 +4590,7 @@
         <v>8.1426906980753937E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -4654,7 +4660,7 @@
         <v>-1.3857309301924612E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>36</v>
       </c>
@@ -4724,7 +4730,7 @@
         <v>9.9142690698075398E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -4794,7 +4800,7 @@
         <v>-1.048573093019246E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -4864,7 +4870,7 @@
         <v>-7.8857309301924618E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>33</v>
       </c>
